--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0001T0006Z000C1N35_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0001T0006Z000C1N35_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>84.59438869949125</v>
+        <v>13.74658816366733</v>
       </c>
       <c r="D2" t="n">
-        <v>80.30144743431347</v>
+        <v>13.04898520807594</v>
       </c>
       <c r="E2" t="n">
-        <v>22.61495011469808</v>
+        <v>3.674929393638438</v>
       </c>
       <c r="F2" t="n">
-        <v>21.39097486210604</v>
+        <v>3.476033415092231</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>73.64529406051987</v>
+        <v>11.96736028483448</v>
       </c>
       <c r="D3" t="n">
-        <v>69.21364985107307</v>
+        <v>11.24721810079937</v>
       </c>
       <c r="E3" t="n">
-        <v>22.61495011469808</v>
+        <v>3.674929393638438</v>
       </c>
       <c r="F3" t="n">
-        <v>21.39097486210604</v>
+        <v>3.476033415092231</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.46391017945595</v>
+        <v>4.300385404161593</v>
       </c>
       <c r="D4" t="n">
-        <v>24.12416831335366</v>
+        <v>3.920177350919969</v>
       </c>
       <c r="E4" t="n">
-        <v>22.61495011469808</v>
+        <v>3.674929393638438</v>
       </c>
       <c r="F4" t="n">
-        <v>21.39097486210604</v>
+        <v>3.476033415092231</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>44.75398621684145</v>
+        <v>7.272522760236736</v>
       </c>
       <c r="D5" t="n">
-        <v>42.03686737017203</v>
+        <v>6.830990947652955</v>
       </c>
       <c r="E5" t="n">
-        <v>22.61495011469808</v>
+        <v>3.674929393638438</v>
       </c>
       <c r="F5" t="n">
-        <v>21.39097486210604</v>
+        <v>3.476033415092231</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.14679277913629</v>
+        <v>6.686353826609648</v>
       </c>
       <c r="D6" t="n">
-        <v>28.2842712474619</v>
+        <v>4.59619407771256</v>
       </c>
       <c r="E6" t="n">
-        <v>22.61495011469808</v>
+        <v>3.674929393638438</v>
       </c>
       <c r="F6" t="n">
-        <v>21.39097486210604</v>
+        <v>3.476033415092231</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>60.10400159552064</v>
+        <v>9.766900259272104</v>
       </c>
       <c r="D7" t="n">
-        <v>27.47664261375559</v>
+        <v>4.464954424735284</v>
       </c>
       <c r="E7" t="n">
-        <v>22.61495011469808</v>
+        <v>3.674929393638438</v>
       </c>
       <c r="F7" t="n">
-        <v>21.39097486210604</v>
+        <v>3.476033415092231</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.16074745300661</v>
+        <v>5.551121461113574</v>
       </c>
       <c r="D8" t="n">
-        <v>29.26174977679906</v>
+        <v>4.755034338729848</v>
       </c>
       <c r="E8" t="n">
-        <v>22.61495011469808</v>
+        <v>3.674929393638438</v>
       </c>
       <c r="F8" t="n">
-        <v>21.39097486210604</v>
+        <v>3.476033415092231</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>65.8099217433824</v>
+        <v>10.69411228329964</v>
       </c>
       <c r="D9" t="n">
-        <v>9.974406377656614</v>
+        <v>1.6208410363692</v>
       </c>
       <c r="E9" t="n">
-        <v>22.61495011469808</v>
+        <v>3.674929393638438</v>
       </c>
       <c r="F9" t="n">
-        <v>21.39097486210604</v>
+        <v>3.476033415092231</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>57.91638216480954</v>
+        <v>9.411412101781551</v>
       </c>
       <c r="D10" t="n">
-        <v>2.930526021020832</v>
+        <v>0.4762104784158852</v>
       </c>
       <c r="E10" t="n">
-        <v>22.61495011469808</v>
+        <v>3.674929393638438</v>
       </c>
       <c r="F10" t="n">
-        <v>21.39097486210604</v>
+        <v>3.476033415092231</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>68.53165677035744</v>
+        <v>11.13639422518309</v>
       </c>
       <c r="D11" t="n">
-        <v>20.043915594278</v>
+        <v>3.257136284070176</v>
       </c>
       <c r="E11" t="n">
-        <v>22.61495011469808</v>
+        <v>3.674929393638438</v>
       </c>
       <c r="F11" t="n">
-        <v>21.39097486210604</v>
+        <v>3.476033415092231</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>86.38554328313407</v>
+        <v>14.03765078350929</v>
       </c>
       <c r="D12" t="n">
-        <v>23.75606284934111</v>
+        <v>3.86036021301793</v>
       </c>
       <c r="E12" t="n">
-        <v>22.61495011469808</v>
+        <v>3.674929393638438</v>
       </c>
       <c r="F12" t="n">
-        <v>21.39097486210604</v>
+        <v>3.476033415092231</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>107.3074614920162</v>
+        <v>17.43746249245263</v>
       </c>
       <c r="D13" t="n">
-        <v>38.21681212325252</v>
+        <v>6.210231970028534</v>
       </c>
       <c r="E13" t="n">
-        <v>22.61495011469808</v>
+        <v>3.674929393638438</v>
       </c>
       <c r="F13" t="n">
-        <v>21.39097486210604</v>
+        <v>3.476033415092231</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
